--- a/doc/kv_script_Pos_info.xlsx
+++ b/doc/kv_script_Pos_info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83ACFCD8-1CED-444C-9557-836157767CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BF3765-0AD0-4226-8730-BA46E572BC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -841,7 +841,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -935,35 +935,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="lightUp">
           <fgColor rgb="FF33CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor rgb="FF33CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1450,7 +1430,7 @@
       <c r="A2" s="27">
         <v>38</v>
       </c>
-      <c r="B2" s="31"/>
+      <c r="B2" s="2"/>
       <c r="C2" s="27">
         <v>1</v>
       </c>
@@ -2018,7 +1998,7 @@
         <v>4</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" ref="E18:E49" si="12">E17+1</f>
+        <f t="shared" ref="E18" si="12">E17+1</f>
         <v>2</v>
       </c>
       <c r="F18" s="5"/>
@@ -2193,7 +2173,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" ref="E23:E54" si="16">E22+1</f>
+        <f t="shared" ref="E23" si="16">E22+1</f>
         <v>2</v>
       </c>
       <c r="F23" s="5"/>
@@ -2368,7 +2348,7 @@
         <v>6</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" ref="E28:E59" si="20">E27+1</f>
+        <f t="shared" ref="E28" si="20">E27+1</f>
         <v>2</v>
       </c>
       <c r="F28" s="9"/>
@@ -2543,7 +2523,7 @@
         <v>7</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" ref="E33:E64" si="24">E32+1</f>
+        <f t="shared" ref="E33" si="24">E32+1</f>
         <v>2</v>
       </c>
       <c r="F33" s="9"/>
@@ -2673,7 +2653,7 @@
       <c r="A37" s="26">
         <v>12</v>
       </c>
-      <c r="B37" s="32"/>
+      <c r="B37" s="4"/>
       <c r="C37" s="26">
         <f t="shared" ref="C37" si="25">C32+1</f>
         <v>8</v>
@@ -2708,7 +2688,7 @@
       <c r="A38" s="26">
         <v>16</v>
       </c>
-      <c r="B38" s="32"/>
+      <c r="B38" s="4"/>
       <c r="C38" s="26">
         <f t="shared" ref="C38" si="27">C37</f>
         <v>8</v>
@@ -2718,7 +2698,7 @@
         <v>8</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" ref="E38:E69" si="28">E37+1</f>
+        <f t="shared" ref="E38" si="28">E37+1</f>
         <v>2</v>
       </c>
       <c r="F38" s="11"/>
@@ -2743,7 +2723,7 @@
       <c r="A39" s="26">
         <v>17</v>
       </c>
-      <c r="B39" s="32"/>
+      <c r="B39" s="4"/>
       <c r="C39" s="26">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -2893,7 +2873,7 @@
         <v>9</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" ref="E43:E74" si="32">E42+1</f>
+        <f t="shared" ref="E43" si="32">E42+1</f>
         <v>2</v>
       </c>
       <c r="F43" s="5"/>
@@ -3064,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" ref="E48:E79" si="36">E47+1</f>
+        <f t="shared" ref="E48" si="36">E47+1</f>
         <v>2</v>
       </c>
       <c r="F48" s="5"/>
@@ -3229,7 +3209,7 @@
         <v>11</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" ref="E53:E96" si="40">E52+1</f>
+        <f t="shared" ref="E53" si="40">E52+1</f>
         <v>2</v>
       </c>
       <c r="F53" s="5"/>
@@ -3394,7 +3374,7 @@
         <v>12</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" ref="E58:E96" si="44">E57+1</f>
+        <f t="shared" ref="E58" si="44">E57+1</f>
         <v>2</v>
       </c>
       <c r="F58" s="5"/>
@@ -3551,7 +3531,7 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
-        <f t="shared" ref="C63:C96" si="47">C62</f>
+        <f t="shared" ref="C63:C93" si="47">C62</f>
         <v>13</v>
       </c>
       <c r="D63" s="4" t="str">
@@ -3559,7 +3539,7 @@
         <v>13</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" ref="E63:E96" si="48">E62+1</f>
+        <f t="shared" ref="E63" si="48">E62+1</f>
         <v>2</v>
       </c>
       <c r="F63" s="5"/>
@@ -3724,7 +3704,7 @@
         <v>14</v>
       </c>
       <c r="E68" s="4">
-        <f t="shared" ref="E68:E96" si="51">E67+1</f>
+        <f t="shared" ref="E68" si="51">E67+1</f>
         <v>2</v>
       </c>
       <c r="F68" s="5"/>
@@ -3885,7 +3865,7 @@
         <v>15</v>
       </c>
       <c r="E73" s="4">
-        <f t="shared" ref="E73:E96" si="53">E72+1</f>
+        <f t="shared" ref="E73" si="53">E72+1</f>
         <v>2</v>
       </c>
       <c r="F73" s="5"/>
@@ -4175,7 +4155,7 @@
         <v>17</v>
       </c>
       <c r="E83" s="4">
-        <f t="shared" ref="E83:E96" si="57">E82+1</f>
+        <f t="shared" ref="E83" si="57">E82+1</f>
         <v>2</v>
       </c>
       <c r="F83" s="5"/>
@@ -4320,7 +4300,7 @@
         <v>18</v>
       </c>
       <c r="E88" s="4">
-        <f t="shared" ref="E88:E96" si="59">E87+1</f>
+        <f t="shared" ref="E88" si="59">E87+1</f>
         <v>2</v>
       </c>
       <c r="F88" s="5"/>
@@ -4467,7 +4447,7 @@
         <v>19</v>
       </c>
       <c r="E93" s="4">
-        <f t="shared" ref="E93:E96" si="61">E92+1</f>
+        <f t="shared" ref="E93" si="61">E92+1</f>
         <v>2</v>
       </c>
       <c r="F93" s="5"/>
@@ -4821,7 +4801,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]Sheet1</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5233,10 +5213,10 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]Sheet1 によって生成されました。</v>
       </c>
       <c r="F5">
-        <f t="shared" ref="F5:G68" si="1">F4</f>
+        <f t="shared" ref="F5:F68" si="1">F4</f>
         <v>1</v>
       </c>
       <c r="G5" t="str">
@@ -6877,7 +6857,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]Sheet1 によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//待機位置
@@ -10883,7 +10863,7 @@
         <v>67</v>
       </c>
       <c r="F28">
-        <f t="shared" ref="F28:G28" si="2">F23+1</f>
+        <f t="shared" ref="F28" si="2">F23+1</f>
         <v>6</v>
       </c>
       <c r="G28" t="str">
@@ -11905,7 +11885,7 @@
     </row>
     <row r="33" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F33">
-        <f t="shared" ref="F33:G33" si="3">F28+1</f>
+        <f t="shared" ref="F33" si="3">F28+1</f>
         <v>7</v>
       </c>
       <c r="G33" t="str">
@@ -12921,7 +12901,7 @@
     </row>
     <row r="38" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F38">
-        <f t="shared" ref="F38:G38" si="4">F33+1</f>
+        <f t="shared" ref="F38" si="4">F33+1</f>
         <v>8</v>
       </c>
       <c r="G38" t="str">
@@ -13937,7 +13917,7 @@
     </row>
     <row r="43" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F43">
-        <f t="shared" ref="F43:G43" si="5">F38+1</f>
+        <f t="shared" ref="F43" si="5">F38+1</f>
         <v>9</v>
       </c>
       <c r="G43" t="str">
@@ -14953,7 +14933,7 @@
     </row>
     <row r="48" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F48">
-        <f t="shared" ref="F48:G48" si="6">F43+1</f>
+        <f t="shared" ref="F48" si="6">F43+1</f>
         <v>10</v>
       </c>
       <c r="G48" t="str">
@@ -15969,7 +15949,7 @@
     </row>
     <row r="53" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F53">
-        <f t="shared" ref="F53:G53" si="7">F48+1</f>
+        <f t="shared" ref="F53" si="7">F48+1</f>
         <v>11</v>
       </c>
       <c r="G53" t="str">
@@ -16985,7 +16965,7 @@
     </row>
     <row r="58" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F58">
-        <f t="shared" ref="F58:G58" si="8">F53+1</f>
+        <f t="shared" ref="F58" si="8">F53+1</f>
         <v>12</v>
       </c>
       <c r="G58" t="str">
@@ -18001,7 +17981,7 @@
     </row>
     <row r="63" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F63">
-        <f t="shared" ref="F63:G63" si="9">F58+1</f>
+        <f t="shared" ref="F63" si="9">F58+1</f>
         <v>13</v>
       </c>
       <c r="G63" t="str">
@@ -19113,7 +19093,7 @@
     </row>
     <row r="69" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F69">
-        <f t="shared" ref="F69:G132" si="11">F68</f>
+        <f t="shared" ref="F69:F132" si="11">F68</f>
         <v>13</v>
       </c>
       <c r="G69" t="str">
@@ -25641,7 +25621,7 @@
     </row>
     <row r="133" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F133">
-        <f t="shared" ref="F133:G196" si="13">F132</f>
+        <f t="shared" ref="F133:F196" si="13">F132</f>
         <v>13</v>
       </c>
       <c r="G133" t="str">
@@ -32169,7 +32149,7 @@
     </row>
     <row r="197" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F197">
-        <f t="shared" ref="F197:G202" si="15">F196</f>
+        <f t="shared" ref="F197:F202" si="15">F196</f>
         <v>13</v>
       </c>
       <c r="G197" t="str">
@@ -32788,7 +32768,7 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]Sheet1 によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//待機位置
@@ -33713,5 +33693,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/doc/kv_script_Pos_info.xlsx
+++ b/doc/kv_script_Pos_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3584621-C716-444C-96B5-86CB9DA8CF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A205974-7C0A-4606-A30B-F283A1ADD281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="106">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -631,6 +631,19 @@
   </si>
   <si>
     <t>Winding position</t>
+  </si>
+  <si>
+    <t>補助位置</t>
+    <rPh sb="0" eb="2">
+      <t>ホジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Auxiliary position</t>
   </si>
 </sst>
 </file>
@@ -4170,8 +4183,12 @@
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
-      <c r="H82" s="5"/>
-      <c r="I82" s="5"/>
+      <c r="H82" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>83</v>
+      </c>
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
       <c r="L82" s="5"/>
@@ -4199,8 +4216,12 @@
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
-      <c r="I83" s="5"/>
+      <c r="H83" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="J83" s="5"/>
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
@@ -4840,7 +4861,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5252,7 +5273,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F67" si="1">F4</f>
@@ -6896,7 +6917,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//待機位置
@@ -7877,6 +7898,76 @@
 	ELSE
 		uiErrCode	:= 2;
 	END_IF;
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【171】 待機位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【172】 補助位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【173】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【175】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;
 ELSE
 	uiErrCode	:= 1;
 END_IF;
@@ -19931,7 +20022,7 @@
         <v>5</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>●</v>
       </c>
       <c r="J72">
         <v>70</v>
@@ -20094,7 +20185,10 @@
 			strRt	:= 'unknown';
 		ELSE
 			uiErrCode	:= 3;
-		END_IF;</v>
+		END_IF;
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;</v>
       </c>
       <c r="AM72" t="str">
         <f ca="1"/>
@@ -20111,45 +20205,47 @@
 			strRt	:= 'unknown';
 		ELSE
 			uiErrCode	:= 3;
-		END_IF;</v>
+		END_IF;
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;</v>
       </c>
     </row>
     <row r="73" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F73">
-        <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G73" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H73">
         <f>COUNTIF(G$3:G73,G73)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I73" t="str">
         <v/>
       </c>
-      <c r="J73" t="str">
-        <v/>
+      <c r="J73">
+        <v>81</v>
       </c>
       <c r="K73" t="str">
         <f ca="1"/>
-        <v/>
+        <v>待機位置</v>
       </c>
       <c r="L73" t="str">
         <f ca="1"/>
-        <v/>
+        <v>待機位置</v>
       </c>
       <c r="N73" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【171】 待機位置</v>
       </c>
       <c r="O73" t="str">
         <v/>
       </c>
       <c r="P73" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q73" t="str">
         <f ca="1"/>
@@ -20157,101 +20253,221 @@
       </c>
       <c r="R73" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17</v>
       </c>
       <c r="AA73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN</v>
       </c>
       <c r="AB73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';</v>
       </c>
       <c r="AE73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【171】 待機位置';</v>
       </c>
       <c r="AG73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【171】 待機位置';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【171】 待機位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【171】 待機位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【171】 待機位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【171】 待機位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【171】 待機位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM73" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【171】 待機位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="74" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F74">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G74" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H74">
         <f>COUNTIF(G$3:G74,G74)</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I74" t="str">
         <v/>
       </c>
-      <c r="J74" t="str">
-        <v/>
+      <c r="J74">
+        <v>82</v>
       </c>
       <c r="K74" t="str">
         <f ca="1"/>
-        <v/>
+        <v>補助位置</v>
       </c>
       <c r="L74" t="str">
         <f ca="1"/>
-        <v/>
+        <v>補助位置</v>
       </c>
       <c r="N74" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【172】 補助位置</v>
       </c>
       <c r="O74" t="str">
         <v/>
       </c>
       <c r="P74" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q74" t="str">
         <f ca="1"/>
@@ -20259,83 +20475,178 @@
       </c>
       <c r="R74" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';</v>
       </c>
       <c r="AE74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【172】 補助位置';</v>
       </c>
       <c r="AG74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【172】 補助位置';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【172】 補助位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【172】 補助位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【172】 補助位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【172】 補助位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【172】 補助位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM74" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【172】 補助位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="75" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F75">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G75" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H75">
         <f>COUNTIF(G$3:G75,G75)</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I75" t="str">
         <v/>
       </c>
-      <c r="J75" t="str">
-        <v/>
+      <c r="J75">
+        <v>83</v>
       </c>
       <c r="K75" t="str">
         <f ca="1"/>
@@ -20343,17 +20654,17 @@
       </c>
       <c r="L75" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="N75" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【173】 unknown</v>
       </c>
       <c r="O75" t="str">
         <v/>
       </c>
       <c r="P75" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q75" t="str">
         <f ca="1"/>
@@ -20361,83 +20672,178 @@
       </c>
       <c r="R75" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AE75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【173】 unknown';</v>
       </c>
       <c r="AG75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【173】 unknown';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【173】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【173】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【173】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【173】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【173】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM75" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【173】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="76" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F76">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G76" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H76">
         <f>COUNTIF(G$3:G76,G76)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I76" t="str">
         <v/>
       </c>
-      <c r="J76" t="str">
-        <v/>
+      <c r="J76">
+        <v>84</v>
       </c>
       <c r="K76" t="str">
         <f ca="1"/>
@@ -20445,17 +20851,17 @@
       </c>
       <c r="L76" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="N76" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【174】 unknown</v>
       </c>
       <c r="O76" t="str">
         <v/>
       </c>
       <c r="P76" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q76" t="str">
         <f ca="1"/>
@@ -20463,83 +20869,178 @@
       </c>
       <c r="R76" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AE76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 unknown';</v>
       </c>
       <c r="AG76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 unknown';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM76" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="77" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F77">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G77" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H77">
         <f>COUNTIF(G$3:G77,G77)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I77" t="str">
         <v/>
       </c>
-      <c r="J77" t="str">
-        <v/>
+      <c r="J77">
+        <v>85</v>
       </c>
       <c r="K77" t="str">
         <f ca="1"/>
@@ -20547,17 +21048,17 @@
       </c>
       <c r="L77" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="N77" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【175】 unknown</v>
       </c>
       <c r="O77" t="str">
         <v/>
       </c>
       <c r="P77" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q77" t="str">
         <f ca="1"/>
@@ -20565,77 +21066,172 @@
       </c>
       <c r="R77" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AE77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【175】 unknown';</v>
       </c>
       <c r="AG77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【175】 unknown';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【175】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【175】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【175】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【175】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【175】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM77" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【175】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="78" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F78">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G78" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H78">
         <f>COUNTIF(G$3:G78,G78)</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -20729,15 +21325,15 @@
     <row r="79" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F79">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G79" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H79">
         <f>COUNTIF(G$3:G79,G79)</f>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -20831,15 +21427,15 @@
     <row r="80" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F80">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G80" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H80">
         <f>COUNTIF(G$3:G80,G80)</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -20933,15 +21529,15 @@
     <row r="81" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F81">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G81" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H81">
         <f>COUNTIF(G$3:G81,G81)</f>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -21035,15 +21631,15 @@
     <row r="82" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F82">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G82" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H82">
         <f>COUNTIF(G$3:G82,G82)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -21137,15 +21733,15 @@
     <row r="83" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F83">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G83" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H83">
         <f>COUNTIF(G$3:G83,G83)</f>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -21239,15 +21835,15 @@
     <row r="84" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F84">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G84" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H84">
         <f>COUNTIF(G$3:G84,G84)</f>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -21341,15 +21937,15 @@
     <row r="85" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F85">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G85" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H85">
         <f>COUNTIF(G$3:G85,G85)</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -21443,15 +22039,15 @@
     <row r="86" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F86">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G86" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H86">
         <f>COUNTIF(G$3:G86,G86)</f>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -21545,15 +22141,15 @@
     <row r="87" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F87">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G87" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H87">
         <f>COUNTIF(G$3:G87,G87)</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -21647,15 +22243,15 @@
     <row r="88" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F88">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G88" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H88">
         <f>COUNTIF(G$3:G88,G88)</f>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -21749,15 +22345,15 @@
     <row r="89" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F89">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G89" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H89">
         <f>COUNTIF(G$3:G89,G89)</f>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -21851,15 +22447,15 @@
     <row r="90" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F90">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G90" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H90">
         <f>COUNTIF(G$3:G90,G90)</f>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -21953,15 +22549,15 @@
     <row r="91" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F91">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G91" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H91">
         <f>COUNTIF(G$3:G91,G91)</f>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -22055,15 +22651,15 @@
     <row r="92" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F92">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G92" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H92">
         <f>COUNTIF(G$3:G92,G92)</f>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -22157,15 +22753,15 @@
     <row r="93" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F93">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G93" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H93">
         <f>COUNTIF(G$3:G93,G93)</f>
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -22259,15 +22855,15 @@
     <row r="94" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F94">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G94" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H94">
         <f>COUNTIF(G$3:G94,G94)</f>
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -22361,15 +22957,15 @@
     <row r="95" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F95">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G95" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H95">
         <f>COUNTIF(G$3:G95,G95)</f>
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -22463,15 +23059,15 @@
     <row r="96" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F96">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G96" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H96">
         <f>COUNTIF(G$3:G96,G96)</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -22565,15 +23161,15 @@
     <row r="97" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F97">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G97" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H97">
         <f>COUNTIF(G$3:G97,G97)</f>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -22667,15 +23263,15 @@
     <row r="98" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F98">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G98" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H98">
         <f>COUNTIF(G$3:G98,G98)</f>
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -22769,15 +23365,15 @@
     <row r="99" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F99">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G99" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H99">
         <f>COUNTIF(G$3:G99,G99)</f>
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -22871,15 +23467,15 @@
     <row r="100" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F100">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G100" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H100">
         <f>COUNTIF(G$3:G100,G100)</f>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -22973,15 +23569,15 @@
     <row r="101" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F101">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G101" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H101">
         <f>COUNTIF(G$3:G101,G101)</f>
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -23075,15 +23671,15 @@
     <row r="102" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F102">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G102" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H102">
         <f>COUNTIF(G$3:G102,G102)</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -23177,15 +23773,15 @@
     <row r="103" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F103">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G103" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H103">
         <f>COUNTIF(G$3:G103,G103)</f>
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -23279,15 +23875,15 @@
     <row r="104" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F104">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G104" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H104">
         <f>COUNTIF(G$3:G104,G104)</f>
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -23381,15 +23977,15 @@
     <row r="105" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F105">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G105" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H105">
         <f>COUNTIF(G$3:G105,G105)</f>
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -23483,15 +24079,15 @@
     <row r="106" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F106">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G106" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H106">
         <f>COUNTIF(G$3:G106,G106)</f>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -23585,15 +24181,15 @@
     <row r="107" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F107">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G107" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H107">
         <f>COUNTIF(G$3:G107,G107)</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -23687,15 +24283,15 @@
     <row r="108" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F108">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G108" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H108">
         <f>COUNTIF(G$3:G108,G108)</f>
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -23789,15 +24385,15 @@
     <row r="109" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F109">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G109" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H109">
         <f>COUNTIF(G$3:G109,G109)</f>
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -23891,15 +24487,15 @@
     <row r="110" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F110">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G110" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H110">
         <f>COUNTIF(G$3:G110,G110)</f>
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -23993,15 +24589,15 @@
     <row r="111" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F111">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G111" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H111">
         <f>COUNTIF(G$3:G111,G111)</f>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I111" t="str">
         <v/>
@@ -24095,15 +24691,15 @@
     <row r="112" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F112">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G112" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H112">
         <f>COUNTIF(G$3:G112,G112)</f>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -24197,15 +24793,15 @@
     <row r="113" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F113">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G113" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H113">
         <f>COUNTIF(G$3:G113,G113)</f>
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -24299,15 +24895,15 @@
     <row r="114" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F114">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G114" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H114">
         <f>COUNTIF(G$3:G114,G114)</f>
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -24401,15 +24997,15 @@
     <row r="115" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F115">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G115" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H115">
         <f>COUNTIF(G$3:G115,G115)</f>
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I115" t="str">
         <v/>
@@ -24503,15 +25099,15 @@
     <row r="116" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F116">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G116" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H116">
         <f>COUNTIF(G$3:G116,G116)</f>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I116" t="str">
         <v/>
@@ -24605,15 +25201,15 @@
     <row r="117" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F117">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G117" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H117">
         <f>COUNTIF(G$3:G117,G117)</f>
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -24707,15 +25303,15 @@
     <row r="118" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F118">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G118" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H118">
         <f>COUNTIF(G$3:G118,G118)</f>
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -24809,15 +25405,15 @@
     <row r="119" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F119">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G119" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H119">
         <f>COUNTIF(G$3:G119,G119)</f>
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -24911,15 +25507,15 @@
     <row r="120" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F120">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G120" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H120">
         <f>COUNTIF(G$3:G120,G120)</f>
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -25013,15 +25609,15 @@
     <row r="121" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F121">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G121" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H121">
         <f>COUNTIF(G$3:G121,G121)</f>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -25115,15 +25711,15 @@
     <row r="122" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F122">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G122" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H122">
         <f>COUNTIF(G$3:G122,G122)</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -25217,15 +25813,15 @@
     <row r="123" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F123">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G123" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H123">
         <f>COUNTIF(G$3:G123,G123)</f>
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -25319,15 +25915,15 @@
     <row r="124" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F124">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G124" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H124">
         <f>COUNTIF(G$3:G124,G124)</f>
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -25421,15 +26017,15 @@
     <row r="125" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F125">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G125" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H125">
         <f>COUNTIF(G$3:G125,G125)</f>
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -25523,15 +26119,15 @@
     <row r="126" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F126">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G126" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H126">
         <f>COUNTIF(G$3:G126,G126)</f>
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -25625,15 +26221,15 @@
     <row r="127" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F127">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G127" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H127">
         <f>COUNTIF(G$3:G127,G127)</f>
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -25727,15 +26323,15 @@
     <row r="128" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F128">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G128" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H128">
         <f>COUNTIF(G$3:G128,G128)</f>
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -25829,15 +26425,15 @@
     <row r="129" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F129">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G129" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H129">
         <f>COUNTIF(G$3:G129,G129)</f>
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -25931,15 +26527,15 @@
     <row r="130" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F130">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G130" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H130">
         <f>COUNTIF(G$3:G130,G130)</f>
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -26033,15 +26629,15 @@
     <row r="131" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F131">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G131" t="str">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H131">
         <f>COUNTIF(G$3:G131,G131)</f>
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -26135,15 +26731,15 @@
     <row r="132" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F132">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G132" t="str">
         <f t="shared" ref="G132:G195" si="14">E132&amp;F132</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H132">
         <f>COUNTIF(G$3:G132,G132)</f>
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -26237,15 +26833,15 @@
     <row r="133" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F133">
         <f t="shared" ref="F133:F196" si="15">F132</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G133" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H133">
         <f>COUNTIF(G$3:G133,G133)</f>
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -26339,15 +26935,15 @@
     <row r="134" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F134">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G134" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H134">
         <f>COUNTIF(G$3:G134,G134)</f>
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -26441,15 +27037,15 @@
     <row r="135" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F135">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G135" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H135">
         <f>COUNTIF(G$3:G135,G135)</f>
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -26543,15 +27139,15 @@
     <row r="136" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F136">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G136" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H136">
         <f>COUNTIF(G$3:G136,G136)</f>
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -26645,15 +27241,15 @@
     <row r="137" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F137">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G137" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H137">
         <f>COUNTIF(G$3:G137,G137)</f>
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -26747,15 +27343,15 @@
     <row r="138" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F138">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G138" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H138">
         <f>COUNTIF(G$3:G138,G138)</f>
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="I138" t="str">
         <v/>
@@ -26849,15 +27445,15 @@
     <row r="139" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F139">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G139" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H139">
         <f>COUNTIF(G$3:G139,G139)</f>
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -26951,15 +27547,15 @@
     <row r="140" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F140">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G140" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H140">
         <f>COUNTIF(G$3:G140,G140)</f>
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -27053,15 +27649,15 @@
     <row r="141" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F141">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G141" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H141">
         <f>COUNTIF(G$3:G141,G141)</f>
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -27155,15 +27751,15 @@
     <row r="142" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F142">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G142" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H142">
         <f>COUNTIF(G$3:G142,G142)</f>
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I142" t="str">
         <v/>
@@ -27257,15 +27853,15 @@
     <row r="143" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F143">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G143" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H143">
         <f>COUNTIF(G$3:G143,G143)</f>
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -27359,15 +27955,15 @@
     <row r="144" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F144">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G144" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H144">
         <f>COUNTIF(G$3:G144,G144)</f>
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -27461,15 +28057,15 @@
     <row r="145" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F145">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G145" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H145">
         <f>COUNTIF(G$3:G145,G145)</f>
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -27563,15 +28159,15 @@
     <row r="146" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F146">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G146" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H146">
         <f>COUNTIF(G$3:G146,G146)</f>
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -27665,15 +28261,15 @@
     <row r="147" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F147">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G147" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H147">
         <f>COUNTIF(G$3:G147,G147)</f>
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -27767,15 +28363,15 @@
     <row r="148" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F148">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G148" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H148">
         <f>COUNTIF(G$3:G148,G148)</f>
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -27869,15 +28465,15 @@
     <row r="149" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F149">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G149" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H149">
         <f>COUNTIF(G$3:G149,G149)</f>
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -27971,15 +28567,15 @@
     <row r="150" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F150">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G150" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H150">
         <f>COUNTIF(G$3:G150,G150)</f>
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -28073,15 +28669,15 @@
     <row r="151" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F151">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G151" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H151">
         <f>COUNTIF(G$3:G151,G151)</f>
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -28175,15 +28771,15 @@
     <row r="152" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F152">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G152" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H152">
         <f>COUNTIF(G$3:G152,G152)</f>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -28277,15 +28873,15 @@
     <row r="153" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F153">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G153" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H153">
         <f>COUNTIF(G$3:G153,G153)</f>
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -28379,15 +28975,15 @@
     <row r="154" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F154">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G154" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H154">
         <f>COUNTIF(G$3:G154,G154)</f>
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I154" t="str">
         <v/>
@@ -28481,15 +29077,15 @@
     <row r="155" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F155">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G155" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H155">
         <f>COUNTIF(G$3:G155,G155)</f>
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I155" t="str">
         <v/>
@@ -28583,15 +29179,15 @@
     <row r="156" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F156">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G156" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H156">
         <f>COUNTIF(G$3:G156,G156)</f>
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -28685,15 +29281,15 @@
     <row r="157" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F157">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G157" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H157">
         <f>COUNTIF(G$3:G157,G157)</f>
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I157" t="str">
         <v/>
@@ -28787,15 +29383,15 @@
     <row r="158" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F158">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G158" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H158">
         <f>COUNTIF(G$3:G158,G158)</f>
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I158" t="str">
         <v/>
@@ -28889,15 +29485,15 @@
     <row r="159" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F159">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G159" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H159">
         <f>COUNTIF(G$3:G159,G159)</f>
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -28991,15 +29587,15 @@
     <row r="160" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F160">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G160" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H160">
         <f>COUNTIF(G$3:G160,G160)</f>
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -29093,15 +29689,15 @@
     <row r="161" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F161">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G161" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H161">
         <f>COUNTIF(G$3:G161,G161)</f>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -29195,15 +29791,15 @@
     <row r="162" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F162">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G162" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H162">
         <f>COUNTIF(G$3:G162,G162)</f>
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I162" t="str">
         <v/>
@@ -29297,15 +29893,15 @@
     <row r="163" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F163">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G163" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H163">
         <f>COUNTIF(G$3:G163,G163)</f>
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -29399,15 +29995,15 @@
     <row r="164" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F164">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G164" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H164">
         <f>COUNTIF(G$3:G164,G164)</f>
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I164" t="str">
         <v/>
@@ -29501,15 +30097,15 @@
     <row r="165" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F165">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G165" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H165">
         <f>COUNTIF(G$3:G165,G165)</f>
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -29603,15 +30199,15 @@
     <row r="166" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F166">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G166" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H166">
         <f>COUNTIF(G$3:G166,G166)</f>
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -29705,15 +30301,15 @@
     <row r="167" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F167">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G167" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H167">
         <f>COUNTIF(G$3:G167,G167)</f>
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I167" t="str">
         <v/>
@@ -29807,15 +30403,15 @@
     <row r="168" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F168">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G168" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H168">
         <f>COUNTIF(G$3:G168,G168)</f>
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I168" t="str">
         <v/>
@@ -29909,15 +30505,15 @@
     <row r="169" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F169">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G169" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H169">
         <f>COUNTIF(G$3:G169,G169)</f>
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -30011,15 +30607,15 @@
     <row r="170" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F170">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G170" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H170">
         <f>COUNTIF(G$3:G170,G170)</f>
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I170" t="str">
         <v/>
@@ -30113,15 +30709,15 @@
     <row r="171" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F171">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G171" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H171">
         <f>COUNTIF(G$3:G171,G171)</f>
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I171" t="str">
         <v/>
@@ -30215,15 +30811,15 @@
     <row r="172" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F172">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G172" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H172">
         <f>COUNTIF(G$3:G172,G172)</f>
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I172" t="str">
         <v/>
@@ -30317,15 +30913,15 @@
     <row r="173" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F173">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G173" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H173">
         <f>COUNTIF(G$3:G173,G173)</f>
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I173" t="str">
         <v/>
@@ -30419,15 +31015,15 @@
     <row r="174" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F174">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G174" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H174">
         <f>COUNTIF(G$3:G174,G174)</f>
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I174" t="str">
         <v/>
@@ -30521,15 +31117,15 @@
     <row r="175" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F175">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G175" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H175">
         <f>COUNTIF(G$3:G175,G175)</f>
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -30623,15 +31219,15 @@
     <row r="176" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F176">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G176" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H176">
         <f>COUNTIF(G$3:G176,G176)</f>
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I176" t="str">
         <v/>
@@ -30725,15 +31321,15 @@
     <row r="177" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F177">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G177" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H177">
         <f>COUNTIF(G$3:G177,G177)</f>
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I177" t="str">
         <v/>
@@ -30827,15 +31423,15 @@
     <row r="178" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F178">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G178" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H178">
         <f>COUNTIF(G$3:G178,G178)</f>
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -30929,15 +31525,15 @@
     <row r="179" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F179">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G179" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H179">
         <f>COUNTIF(G$3:G179,G179)</f>
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I179" t="str">
         <v/>
@@ -31031,15 +31627,15 @@
     <row r="180" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F180">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G180" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H180">
         <f>COUNTIF(G$3:G180,G180)</f>
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -31133,15 +31729,15 @@
     <row r="181" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F181">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G181" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H181">
         <f>COUNTIF(G$3:G181,G181)</f>
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -31235,15 +31831,15 @@
     <row r="182" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F182">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G182" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H182">
         <f>COUNTIF(G$3:G182,G182)</f>
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I182" t="str">
         <v/>
@@ -31337,15 +31933,15 @@
     <row r="183" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F183">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G183" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H183">
         <f>COUNTIF(G$3:G183,G183)</f>
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -31439,15 +32035,15 @@
     <row r="184" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F184">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G184" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H184">
         <f>COUNTIF(G$3:G184,G184)</f>
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I184" t="str">
         <v/>
@@ -31541,15 +32137,15 @@
     <row r="185" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F185">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G185" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H185">
         <f>COUNTIF(G$3:G185,G185)</f>
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I185" t="str">
         <v/>
@@ -31643,15 +32239,15 @@
     <row r="186" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F186">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G186" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H186">
         <f>COUNTIF(G$3:G186,G186)</f>
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I186" t="str">
         <v/>
@@ -31745,15 +32341,15 @@
     <row r="187" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F187">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G187" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H187">
         <f>COUNTIF(G$3:G187,G187)</f>
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -31847,15 +32443,15 @@
     <row r="188" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F188">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G188" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H188">
         <f>COUNTIF(G$3:G188,G188)</f>
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I188" t="str">
         <v/>
@@ -31949,15 +32545,15 @@
     <row r="189" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F189">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G189" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H189">
         <f>COUNTIF(G$3:G189,G189)</f>
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I189" t="str">
         <v/>
@@ -32051,15 +32647,15 @@
     <row r="190" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F190">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G190" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H190">
         <f>COUNTIF(G$3:G190,G190)</f>
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I190" t="str">
         <v/>
@@ -32153,15 +32749,15 @@
     <row r="191" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F191">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G191" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H191">
         <f>COUNTIF(G$3:G191,G191)</f>
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I191" t="str">
         <v/>
@@ -32255,15 +32851,15 @@
     <row r="192" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F192">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G192" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H192">
         <f>COUNTIF(G$3:G192,G192)</f>
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I192" t="str">
         <v/>
@@ -32357,15 +32953,15 @@
     <row r="193" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F193">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G193" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H193">
         <f>COUNTIF(G$3:G193,G193)</f>
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I193" t="str">
         <v/>
@@ -32459,15 +33055,15 @@
     <row r="194" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F194">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G194" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H194">
         <f>COUNTIF(G$3:G194,G194)</f>
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I194" t="str">
         <v/>
@@ -32561,15 +33157,15 @@
     <row r="195" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F195">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G195" t="str">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H195">
         <f>COUNTIF(G$3:G195,G195)</f>
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I195" t="str">
         <v/>
@@ -32663,15 +33259,15 @@
     <row r="196" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F196">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G196" t="str">
         <f t="shared" ref="G196:G202" si="16">E196&amp;F196</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H196">
         <f>COUNTIF(G$3:G196,G196)</f>
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I196" t="str">
         <v/>
@@ -32765,15 +33361,15 @@
     <row r="197" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F197">
         <f t="shared" ref="F197:F202" si="17">F196</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G197" t="str">
         <f t="shared" si="16"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H197">
         <f>COUNTIF(G$3:G197,G197)</f>
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I197" t="str">
         <v/>
@@ -32867,15 +33463,15 @@
     <row r="198" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F198">
         <f t="shared" si="17"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G198" t="str">
         <f t="shared" si="16"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H198">
         <f>COUNTIF(G$3:G198,G198)</f>
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I198" t="str">
         <v/>
@@ -32969,15 +33565,15 @@
     <row r="199" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F199">
         <f t="shared" si="17"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G199" t="str">
         <f t="shared" si="16"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H199">
         <f>COUNTIF(G$3:G199,G199)</f>
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I199" t="str">
         <v/>
@@ -33071,15 +33667,15 @@
     <row r="200" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F200">
         <f t="shared" si="17"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G200" t="str">
         <f t="shared" si="16"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H200">
         <f>COUNTIF(G$3:G200,G200)</f>
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I200" t="str">
         <v/>
@@ -33173,15 +33769,15 @@
     <row r="201" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F201">
         <f t="shared" si="17"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G201" t="str">
         <f t="shared" si="16"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H201">
         <f>COUNTIF(G$3:G201,G201)</f>
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I201" t="str">
         <v/>
@@ -33275,15 +33871,15 @@
     <row r="202" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F202">
         <f t="shared" si="17"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G202" t="str">
         <f t="shared" si="16"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H202">
         <f>COUNTIF(G$3:G202,G202)</f>
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I202" t="str">
         <v>●</v>
@@ -33383,7 +33979,7 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//待機位置
@@ -34354,6 +34950,76 @@
 			strRt	:= '(予約)';
 		ELSIF strInfoKey = 'index_name' THEN
 			strRt	:= '【145】 (予約)';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;
+//17
+ELSIF strInfoType = 17 THEN
+	//待機位置
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '待機位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【171】 待機位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//補助位置
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '補助位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【172】 補助位置';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//unknown
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【173】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//unknown
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 unknown';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//unknown
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【175】 unknown';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_Pos_info.xlsx
+++ b/doc/kv_script_Pos_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B9F7DC-831E-4F0B-B22F-B56BA10F8E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9723B47-606C-4BE3-86DC-7F531FD3B766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -697,18 +697,20 @@
     <t>(予約)</t>
   </si>
   <si>
-    <t>計測位置</t>
+    <t>計測退避位置</t>
     <rPh sb="0" eb="2">
       <t>ケイソク</t>
     </rPh>
     <rPh sb="2" eb="4">
+      <t>タイヒ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
       <t>イチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Measurement Position</t>
-    <phoneticPr fontId="1"/>
+    <t>Measurement and evacuation position</t>
   </si>
 </sst>
 </file>
@@ -4998,7 +5000,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_index</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5410,7 +5412,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F67" si="1">F4</f>
@@ -7054,7 +7056,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//待機位置
@@ -8076,12 +8078,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【174】 計測位置';
+			strRt	:= '計測退避位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 計測退避位置';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -21054,15 +21056,15 @@
       </c>
       <c r="K76" t="str">
         <f ca="1"/>
-        <v>計測位置</v>
+        <v>計測退避位置</v>
       </c>
       <c r="L76" t="str">
         <f ca="1"/>
-        <v>計測位置</v>
+        <v>計測退避位置</v>
       </c>
       <c r="N76" t="str">
         <f ca="1"/>
-        <v>【174】 計測位置</v>
+        <v>【174】 計測退避位置</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -21091,75 +21093,75 @@
       <c r="AB76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';</v>
+			strRt	:= '計測退避位置';</v>
       </c>
       <c r="AE76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
+			strRt	:= '計測退避位置';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【174】 計測位置';</v>
+			strRt	:= '計測退避位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 計測退避位置';</v>
       </c>
       <c r="AG76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【174】 計測位置';
+			strRt	:= '計測退避位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 計測退避位置';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【174】 計測位置';
+			strRt	:= '計測退避位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 計測退避位置';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【174】 計測位置';
+			strRt	:= '計測退避位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 計測退避位置';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -21167,12 +21169,12 @@
       <c r="AJ76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【174】 計測位置';
+			strRt	:= '計測退避位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 計測退避位置';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -21181,12 +21183,12 @@
       <c r="AK76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【174】 計測位置';
+			strRt	:= '計測退避位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 計測退避位置';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -21198,12 +21200,12 @@
       <c r="AL76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【174】 計測位置';
+			strRt	:= '計測退避位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 計測退避位置';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -21215,12 +21217,12 @@
       <c r="AM76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【174】 計測位置';
+			strRt	:= '計測退避位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 計測退避位置';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -34691,7 +34693,7 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//待機位置
@@ -35713,12 +35715,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//計測位置
+	//計測退避位置
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測位置';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【174】 計測位置';
+			strRt	:= '計測退避位置';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【174】 計測退避位置';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_Pos_info.xlsx
+++ b/doc/kv_script_Pos_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6256DDC-C3C2-4590-80F8-43071D9C62F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698ECA53-0FF8-4C9E-B39B-333040C0C618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="122">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -739,6 +739,14 @@
   <si>
     <t>Welding3 Position</t>
   </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>axis</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -1095,15 +1103,15 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="lightUp">
-          <fgColor rgb="FF33CCCC"/>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <patternFill patternType="lightUp">
+          <fgColor rgb="FF33CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1200,7 +1208,7 @@
               <a:ea typeface="游ゴシック"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t>51</a:t>
+            <a:t>95</a:t>
           </a:fld>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="600"/>
         </a:p>
@@ -1524,10 +1532,12 @@
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="18" t="s">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
+      <c r="C1" s="18" t="s">
+        <v>121</v>
+      </c>
       <c r="D1" s="18" t="s">
         <v>11</v>
       </c>
@@ -1574,7 +1584,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="27">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="27">
@@ -1607,7 +1617,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4">
@@ -1642,7 +1652,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4">
@@ -1677,7 +1687,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4">
@@ -1712,7 +1722,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4">
@@ -1747,7 +1757,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4">
@@ -1782,7 +1792,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4">
@@ -1817,7 +1827,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4">
@@ -1852,7 +1862,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4">
@@ -1887,7 +1897,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4">
@@ -1922,7 +1932,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4">
@@ -1957,7 +1967,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4">
@@ -1992,7 +2002,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4">
@@ -2027,7 +2037,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4">
@@ -2062,7 +2072,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4">
@@ -2097,7 +2107,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4">
@@ -2132,7 +2142,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4">
@@ -2167,7 +2177,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="4">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4">
@@ -2202,7 +2212,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4">
@@ -2237,7 +2247,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4">
@@ -2272,7 +2282,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4">
@@ -2307,7 +2317,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4">
@@ -2342,7 +2352,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4">
@@ -2377,7 +2387,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4">
@@ -2412,7 +2422,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4">
@@ -2447,7 +2457,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4">
@@ -2482,7 +2492,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4">
@@ -2517,7 +2527,7 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4">
@@ -2552,7 +2562,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
@@ -2587,7 +2597,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4">
@@ -2622,7 +2632,7 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4">
@@ -2657,7 +2667,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4">
@@ -2692,7 +2702,7 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4">
@@ -2727,7 +2737,7 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="4">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4">
@@ -2762,7 +2772,7 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4">
@@ -2796,8 +2806,8 @@
       <c r="R36" s="7"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="26">
-        <v>12</v>
+      <c r="A37" s="4">
+        <v>35</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="26">
@@ -2831,8 +2841,8 @@
       <c r="R37" s="7"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="26">
-        <v>16</v>
+      <c r="A38" s="4">
+        <v>36</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="26">
@@ -2866,8 +2876,8 @@
       <c r="R38" s="7"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="26">
-        <v>17</v>
+      <c r="A39" s="4">
+        <v>37</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="26">
@@ -2902,7 +2912,7 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
@@ -2937,7 +2947,7 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="4">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
@@ -2972,7 +2982,7 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
@@ -3007,7 +3017,7 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="4">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
@@ -3042,7 +3052,7 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
@@ -3077,7 +3087,7 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
@@ -3112,7 +3122,7 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
@@ -3147,7 +3157,7 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
@@ -3181,7 +3191,9 @@
       <c r="R47" s="7"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="4"/>
+      <c r="A48" s="4">
+        <v>46</v>
+      </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
         <f t="shared" ref="C48" si="32">C43+1</f>
@@ -3214,7 +3226,9 @@
       <c r="R48" s="7"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="4"/>
+      <c r="A49" s="4">
+        <v>47</v>
+      </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
         <f t="shared" ref="C49" si="34">C48</f>
@@ -3247,7 +3261,9 @@
       <c r="R49" s="7"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="4"/>
+      <c r="A50" s="4">
+        <v>48</v>
+      </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
         <f t="shared" si="7"/>
@@ -3280,7 +3296,9 @@
       <c r="R50" s="7"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="4"/>
+      <c r="A51" s="4">
+        <v>49</v>
+      </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
         <f t="shared" si="7"/>
@@ -3313,7 +3331,9 @@
       <c r="R51" s="7"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="4"/>
+      <c r="A52" s="4">
+        <v>50</v>
+      </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
         <f t="shared" si="7"/>
@@ -3346,7 +3366,9 @@
       <c r="R52" s="7"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="4"/>
+      <c r="A53" s="4">
+        <v>51</v>
+      </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
         <f t="shared" ref="C53" si="36">C48+1</f>
@@ -3379,7 +3401,9 @@
       <c r="R53" s="7"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="4"/>
+      <c r="A54" s="4">
+        <v>52</v>
+      </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
         <f t="shared" ref="C54" si="38">C53</f>
@@ -3412,7 +3436,9 @@
       <c r="R54" s="7"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="4"/>
+      <c r="A55" s="4">
+        <v>53</v>
+      </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
         <f t="shared" si="7"/>
@@ -3445,7 +3471,9 @@
       <c r="R55" s="7"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="4"/>
+      <c r="A56" s="4">
+        <v>54</v>
+      </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
         <f t="shared" si="7"/>
@@ -3478,7 +3506,9 @@
       <c r="R56" s="7"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="4"/>
+      <c r="A57" s="4">
+        <v>55</v>
+      </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4">
         <f t="shared" si="7"/>
@@ -3511,7 +3541,9 @@
       <c r="R57" s="7"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="4"/>
+      <c r="A58" s="4">
+        <v>56</v>
+      </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
         <f t="shared" ref="C58" si="40">C53+1</f>
@@ -3544,7 +3576,9 @@
       <c r="R58" s="7"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="4"/>
+      <c r="A59" s="4">
+        <v>57</v>
+      </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
         <f t="shared" ref="C59" si="42">C58</f>
@@ -3577,7 +3611,9 @@
       <c r="R59" s="7"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="4"/>
+      <c r="A60" s="4">
+        <v>58</v>
+      </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
         <f t="shared" si="7"/>
@@ -3610,7 +3646,9 @@
       <c r="R60" s="7"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="4"/>
+      <c r="A61" s="4">
+        <v>59</v>
+      </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
         <f t="shared" si="7"/>
@@ -3643,7 +3681,9 @@
       <c r="R61" s="7"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="4"/>
+      <c r="A62" s="4">
+        <v>60</v>
+      </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
         <f t="shared" si="7"/>
@@ -3676,7 +3716,9 @@
       <c r="R62" s="7"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="4"/>
+      <c r="A63" s="4">
+        <v>61</v>
+      </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
         <f t="shared" ref="C63:C93" si="44">C58+1</f>
@@ -3709,7 +3751,9 @@
       <c r="R63" s="7"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="4"/>
+      <c r="A64" s="4">
+        <v>62</v>
+      </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
         <f t="shared" ref="C64:C94" si="46">C63</f>
@@ -3742,7 +3786,9 @@
       <c r="R64" s="7"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="4"/>
+      <c r="A65" s="4">
+        <v>63</v>
+      </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4">
         <f t="shared" si="7"/>
@@ -3775,7 +3821,9 @@
       <c r="R65" s="7"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="4"/>
+      <c r="A66" s="4">
+        <v>64</v>
+      </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4">
         <f t="shared" si="7"/>
@@ -3808,7 +3856,9 @@
       <c r="R66" s="7"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="4"/>
+      <c r="A67" s="4">
+        <v>65</v>
+      </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4">
         <f t="shared" si="7"/>
@@ -3841,7 +3891,9 @@
       <c r="R67" s="7"/>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="4"/>
+      <c r="A68" s="4">
+        <v>66</v>
+      </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4">
         <f t="shared" si="44"/>
@@ -3874,7 +3926,9 @@
       <c r="R68" s="7"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="4"/>
+      <c r="A69" s="4">
+        <v>67</v>
+      </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4">
         <f t="shared" si="46"/>
@@ -3907,7 +3961,9 @@
       <c r="R69" s="7"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="4"/>
+      <c r="A70" s="4">
+        <v>68</v>
+      </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4">
         <f t="shared" si="7"/>
@@ -3940,7 +3996,9 @@
       <c r="R70" s="7"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="4"/>
+      <c r="A71" s="4">
+        <v>69</v>
+      </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4">
         <f t="shared" si="7"/>
@@ -3973,7 +4031,9 @@
       <c r="R71" s="7"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="4"/>
+      <c r="A72" s="4">
+        <v>70</v>
+      </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4">
         <f t="shared" si="7"/>
@@ -4006,7 +4066,9 @@
       <c r="R72" s="7"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="4"/>
+      <c r="A73" s="4">
+        <v>71</v>
+      </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4">
         <f t="shared" si="44"/>
@@ -4039,7 +4101,9 @@
       <c r="R73" s="7"/>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="4"/>
+      <c r="A74" s="4">
+        <v>72</v>
+      </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4">
         <f t="shared" si="46"/>
@@ -4072,7 +4136,9 @@
       <c r="R74" s="7"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="4"/>
+      <c r="A75" s="4">
+        <v>73</v>
+      </c>
       <c r="B75" s="4"/>
       <c r="C75" s="4">
         <f t="shared" si="7"/>
@@ -4105,7 +4171,9 @@
       <c r="R75" s="7"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="4"/>
+      <c r="A76" s="4">
+        <v>74</v>
+      </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4">
         <f t="shared" si="7"/>
@@ -4138,7 +4206,9 @@
       <c r="R76" s="7"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="4"/>
+      <c r="A77" s="4">
+        <v>75</v>
+      </c>
       <c r="B77" s="4"/>
       <c r="C77" s="4">
         <f t="shared" si="7"/>
@@ -4171,7 +4241,9 @@
       <c r="R77" s="7"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="4"/>
+      <c r="A78" s="4">
+        <v>76</v>
+      </c>
       <c r="B78" s="4"/>
       <c r="C78" s="4">
         <f t="shared" si="44"/>
@@ -4204,7 +4276,9 @@
       <c r="R78" s="7"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="4"/>
+      <c r="A79" s="4">
+        <v>77</v>
+      </c>
       <c r="B79" s="4"/>
       <c r="C79" s="4">
         <f t="shared" si="46"/>
@@ -4237,7 +4311,9 @@
       <c r="R79" s="7"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="4"/>
+      <c r="A80" s="4">
+        <v>78</v>
+      </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4">
         <f t="shared" si="7"/>
@@ -4270,7 +4346,9 @@
       <c r="R80" s="7"/>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="4"/>
+      <c r="A81" s="4">
+        <v>79</v>
+      </c>
       <c r="B81" s="4"/>
       <c r="C81" s="4">
         <f t="shared" si="7"/>
@@ -4303,7 +4381,9 @@
       <c r="R81" s="7"/>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="4"/>
+      <c r="A82" s="4">
+        <v>80</v>
+      </c>
       <c r="B82" s="4"/>
       <c r="C82" s="4">
         <f t="shared" si="7"/>
@@ -4336,7 +4416,9 @@
       <c r="R82" s="7"/>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="4"/>
+      <c r="A83" s="4">
+        <v>81</v>
+      </c>
       <c r="B83" s="4"/>
       <c r="C83" s="4">
         <f t="shared" si="44"/>
@@ -4369,7 +4451,9 @@
       <c r="R83" s="7"/>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="4"/>
+      <c r="A84" s="4">
+        <v>82</v>
+      </c>
       <c r="B84" s="4"/>
       <c r="C84" s="4">
         <f t="shared" si="46"/>
@@ -4402,7 +4486,9 @@
       <c r="R84" s="7"/>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="4"/>
+      <c r="A85" s="4">
+        <v>83</v>
+      </c>
       <c r="B85" s="4"/>
       <c r="C85" s="4">
         <f t="shared" si="7"/>
@@ -4435,7 +4521,9 @@
       <c r="R85" s="7"/>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="4"/>
+      <c r="A86" s="4">
+        <v>84</v>
+      </c>
       <c r="B86" s="4"/>
       <c r="C86" s="4">
         <f t="shared" si="7"/>
@@ -4468,7 +4556,9 @@
       <c r="R86" s="7"/>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="4"/>
+      <c r="A87" s="4">
+        <v>85</v>
+      </c>
       <c r="B87" s="4"/>
       <c r="C87" s="4">
         <f t="shared" si="7"/>
@@ -4501,7 +4591,9 @@
       <c r="R87" s="7"/>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="4"/>
+      <c r="A88" s="4">
+        <v>86</v>
+      </c>
       <c r="B88" s="4"/>
       <c r="C88" s="4">
         <f t="shared" si="44"/>
@@ -4534,7 +4626,9 @@
       <c r="R88" s="7"/>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="4"/>
+      <c r="A89" s="4">
+        <v>87</v>
+      </c>
       <c r="B89" s="4"/>
       <c r="C89" s="4">
         <f t="shared" si="46"/>
@@ -4567,7 +4661,9 @@
       <c r="R89" s="7"/>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="4"/>
+      <c r="A90" s="4">
+        <v>88</v>
+      </c>
       <c r="B90" s="4"/>
       <c r="C90" s="4">
         <f t="shared" si="7"/>
@@ -4600,7 +4696,9 @@
       <c r="R90" s="7"/>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="4"/>
+      <c r="A91" s="4">
+        <v>89</v>
+      </c>
       <c r="B91" s="4"/>
       <c r="C91" s="4">
         <f t="shared" si="7"/>
@@ -4633,7 +4731,9 @@
       <c r="R91" s="7"/>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="4"/>
+      <c r="A92" s="4">
+        <v>90</v>
+      </c>
       <c r="B92" s="4"/>
       <c r="C92" s="4">
         <f t="shared" si="7"/>
@@ -4666,7 +4766,9 @@
       <c r="R92" s="7"/>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="4"/>
+      <c r="A93" s="4">
+        <v>91</v>
+      </c>
       <c r="B93" s="4"/>
       <c r="C93" s="4">
         <f t="shared" si="44"/>
@@ -4696,7 +4798,7 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="4">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4">
@@ -4727,7 +4829,7 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="4">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="4">
@@ -4758,7 +4860,7 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="4">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="4">
@@ -4789,7 +4891,7 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="4">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="4">
@@ -4849,7 +4951,7 @@
     <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <f>MAX(A$2:A$98)</f>
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="F101">
         <f>MAX(F$2:F$98)</f>
@@ -4900,19 +5002,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R97" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R97">
-      <sortCondition ref="D1:D97"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:R97" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}"/>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A2:R98">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5062,7 +5160,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_index</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5474,7 +5572,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -7118,7 +7216,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$206</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//待機位置
@@ -34965,7 +35063,7 @@
     <row r="206" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM206" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$203)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//待機位置
@@ -36108,7 +36206,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/doc/kv_script_Pos_info.xlsx
+++ b/doc/kv_script_Pos_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847FC309-72D5-4B0C-AD07-04572F1A8A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CCA274-27B3-4EC6-8517-A29D88D89A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\event\20260717_1514_言語確認\[表示文字一覧.xlsx]ユニット動作名</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\event\20260717_1514_言語確認\[表示文字一覧.xlsx]ユニット動作名 によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$206</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\event\20260717_1514_言語確認\[表示文字一覧.xlsx]ユニット動作名 によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//Standby Pos
@@ -35796,7 +35796,7 @@
     <row r="206" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM206" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$203)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\event\20260717_1514_言語確認\[表示文字一覧.xlsx]ユニット動作名 によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//Standby Pos
